--- a/data/df_c_c_drugs.xlsx
+++ b/data/df_c_c_drugs.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob.sharepoint.com/teams/grp-Bristol_TAG-MTA-MS/Shared Documents/MTA-MS/Working Folder_HE/MS Models/Git Repo/MS-MTA/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{5814B52A-8B7B-4285-BF54-0F881C7C1987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A149E626-7196-4E84-8188-3755A2D5E8F6}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{5814B52A-8B7B-4285-BF54-0F881C7C1987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2278AA6F-C0A2-49CB-9D90-E7D14E1C196C}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="-14880" windowWidth="21600" windowHeight="11235" xr2:uid="{E0B8145D-B624-45A5-A274-EBB534E327AA}"/>
+    <workbookView xWindow="17745" yWindow="-15525" windowWidth="10890" windowHeight="15375" xr2:uid="{E0B8145D-B624-45A5-A274-EBB534E327AA}"/>
   </bookViews>
   <sheets>
     <sheet name="df_c_c_drugs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -233,7 +246,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +429,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,10 +599,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -634,6 +654,7 @@
   <colors>
     <mruColors>
       <color rgb="FF00FFFF"/>
+      <color rgb="FF00FF00"/>
     </mruColors>
   </colors>
   <extLst>
@@ -966,6 +987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FCE6B58-0091-4096-801E-6027CC3BD0FC}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="2" max="4" width="18.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
@@ -986,13 +1011,13 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>11017.5</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="3">
         <v>11017.5</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="3">
         <v>11017.5</v>
       </c>
     </row>
@@ -1000,13 +1025,13 @@
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="3">
         <v>11017.5</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="3">
         <v>11017.5</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="3">
         <v>11017.5</v>
       </c>
     </row>
@@ -1056,55 +1081,55 @@
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1">
-        <v>35225</v>
-      </c>
-      <c r="C7" s="1">
-        <v>21135</v>
-      </c>
-      <c r="D7" s="1">
-        <v>28180</v>
+      <c r="B7" s="3">
+        <v>32537.5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>19522.5</v>
+      </c>
+      <c r="D7" s="3">
+        <v>26030</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1">
-        <v>26373</v>
-      </c>
-      <c r="C8" s="1">
-        <v>26373</v>
-      </c>
-      <c r="D8" s="1">
-        <v>26373</v>
+      <c r="B8" s="3">
+        <v>23929.486459819072</v>
+      </c>
+      <c r="C8" s="3">
+        <v>23929.486459819072</v>
+      </c>
+      <c r="D8" s="3">
+        <v>23929.486459819072</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="1">
-        <v>7985</v>
-      </c>
-      <c r="C9" s="1">
-        <v>7985</v>
-      </c>
-      <c r="D9" s="1">
-        <v>7985</v>
+      <c r="B9" s="3">
+        <v>7985.4489999999996</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7985.4489999999996</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7985.4489999999996</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1">
-        <v>14607.84375</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B10" s="3">
+        <v>14608.17</v>
+      </c>
+      <c r="C10" s="3">
         <v>11686.275</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="3">
         <v>13147.059380000001</v>
       </c>
     </row>
@@ -1112,14 +1137,14 @@
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1">
-        <v>19500</v>
-      </c>
-      <c r="C11" s="1">
-        <v>19500</v>
-      </c>
-      <c r="D11" s="1">
-        <v>19500</v>
+      <c r="B11" s="3">
+        <v>11999.907999999999</v>
+      </c>
+      <c r="C11" s="3">
+        <v>11999.907999999999</v>
+      </c>
+      <c r="D11" s="3">
+        <v>11999.907999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1140,13 +1165,13 @@
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="3">
         <v>6805.26</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="3">
         <v>6805.26</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="3">
         <v>6805.26</v>
       </c>
     </row>
@@ -1154,13 +1179,13 @@
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="3">
         <v>5264.16</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="3">
         <v>5264.16</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="3">
         <v>5264.16</v>
       </c>
     </row>
@@ -1168,13 +1193,13 @@
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="3">
         <v>6376.5</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="3">
         <v>6376.5</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="3">
         <v>6376.5</v>
       </c>
     </row>
@@ -1196,13 +1221,13 @@
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="3">
         <v>3073.26</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="3">
         <v>3073.26</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="3">
         <v>3073.26</v>
       </c>
     </row>
@@ -1210,13 +1235,13 @@
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>3073.26</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="3">
         <v>3073.26</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>3073.26</v>
       </c>
     </row>

--- a/data/df_c_c_drugs.xlsx
+++ b/data/df_c_c_drugs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob.sharepoint.com/teams/grp-Bristol_TAG-MTA-MS/Shared Documents/MTA-MS/Working Folder_HE/MS Models/Git Repo/MS-MTA/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{5814B52A-8B7B-4285-BF54-0F881C7C1987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2278AA6F-C0A2-49CB-9D90-E7D14E1C196C}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{5814B52A-8B7B-4285-BF54-0F881C7C1987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E547EC65-8E79-48F8-84FD-9AF4C561E298}"/>
   <bookViews>
-    <workbookView xWindow="17745" yWindow="-15525" windowWidth="10890" windowHeight="15375" xr2:uid="{E0B8145D-B624-45A5-A274-EBB534E327AA}"/>
+    <workbookView xWindow="15150" yWindow="-16080" windowWidth="11175" windowHeight="11940" xr2:uid="{E0B8145D-B624-45A5-A274-EBB534E327AA}"/>
   </bookViews>
   <sheets>
     <sheet name="df_c_c_drugs" sheetId="1" r:id="rId1"/>
@@ -68,12 +68,6 @@
     <t>Cladribine</t>
   </si>
   <si>
-    <t>Ponesimod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ofatumumab </t>
-  </si>
-  <si>
     <t>Ocrelizumab</t>
   </si>
   <si>
@@ -96,6 +90,12 @@
   </si>
   <si>
     <t>Glatiramer Acetate 40mg</t>
+  </si>
+  <si>
+    <t>Ofatumumab</t>
+  </si>
+  <si>
+    <t>Ublituximab</t>
   </si>
 </sst>
 </file>
@@ -1107,21 +1107,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3">
-        <v>7985.4489999999996</v>
+        <v>15217.571250000001</v>
       </c>
       <c r="C9" s="3">
-        <v>7985.4489999999996</v>
+        <v>9769.3050000000003</v>
       </c>
       <c r="D9" s="3">
-        <v>7985.4489999999996</v>
+        <v>12493.438125000001</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>14608.17</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3">
         <v>11999.907999999999</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1">
         <v>8502</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3">
         <v>6805.26</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B14" s="3">
         <v>5264.16</v>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3">
         <v>6376.5</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1">
         <v>5067.3</v>
@@ -1219,38 +1219,48 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3">
-        <v>3073.26</v>
+        <v>3237.502</v>
       </c>
       <c r="C17" s="3">
-        <v>3073.26</v>
+        <v>3237.502</v>
       </c>
       <c r="D17" s="3">
-        <v>3073.26</v>
+        <v>3237.502</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3">
-        <v>3073.26</v>
+        <v>3237.502</v>
       </c>
       <c r="C18" s="3">
-        <v>3073.26</v>
+        <v>3237.502</v>
       </c>
       <c r="D18" s="3">
-        <v>3073.26</v>
+        <v>3237.502</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1dd74ed78a59e353fa0bdc00cb9d4ef2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29b19980e720fd97176dcdbc89cda831" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
@@ -1461,15 +1471,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1481,6 +1482,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EFF746E-2FAC-4CAA-83E3-3115861BC3B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBD721C5-550D-48E8-83DB-ED5AAC32F8E6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1499,14 +1508,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EFF746E-2FAC-4CAA-83E3-3115861BC3B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01D9EDB-39A1-4861-A0B6-818C06CD3F0C}">
   <ds:schemaRefs>

--- a/data/df_c_c_drugs.xlsx
+++ b/data/df_c_c_drugs.xlsx
@@ -1261,8 +1261,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1dd74ed78a59e353fa0bdc00cb9d4ef2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29b19980e720fd97176dcdbc89cda831" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="904d962808a52fea145147f501824070">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea18719b0589a0490468c8ade8a27c2" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
     <xsd:import namespace="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
     <xsd:element name="properties">
@@ -1490,22 +1490,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBD721C5-550D-48E8-83DB-ED5AAC32F8E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
-    <ds:schemaRef ds:uri="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59626B20-B473-4344-858A-3AF2D41592D9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
